--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487650_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487650_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>C. CUESTA DE SANTOS</t>
+          <t>A. OLMEDO VELASCO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.6848</v>
+        <v>8.1333</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5178</v>
+        <v>7.444</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1671</v>
+        <v>0.6893</v>
       </c>
       <c r="G2" t="n">
-        <v>5.585</v>
+        <v>2.1299</v>
       </c>
       <c r="H2" t="n">
-        <v>1.7796</v>
+        <v>-1.2457</v>
       </c>
       <c r="I2" t="n">
-        <v>3.8055</v>
+        <v>3.3756</v>
       </c>
       <c r="J2" t="n">
-        <v>6.5</v>
+        <v>3.6532</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6611</v>
+        <v>-0.173</v>
       </c>
       <c r="L2" t="n">
-        <v>3.8389</v>
+        <v>3.8262</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.915</v>
+        <v>-1.5233</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.8816000000000001</v>
+        <v>-1.0727</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0334</v>
+        <v>-0.4505</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9702</v>
+        <v>2.5224</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R2" t="n">
-        <v>1.9403</v>
+        <v>3.4926</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3286</v>
+        <v>-1.9414</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8479</v>
+        <v>-1.0285</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4807</v>
+        <v>-0.9129</v>
       </c>
       <c r="V2" t="n">
-        <v>2.4582</v>
+        <v>5.4223</v>
       </c>
       <c r="W2" t="n">
-        <v>1.8358</v>
+        <v>5.7895</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6224</v>
+        <v>-0.3672</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. OLMEDO VELASCO</t>
+          <t>C. CUESTA DE SANTOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.3937</v>
+        <v>8.036300000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>6.9225</v>
+        <v>6.6784</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4712</v>
+        <v>1.3578</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1299</v>
+        <v>5.585</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2457</v>
+        <v>1.7796</v>
       </c>
       <c r="I3" t="n">
-        <v>3.3756</v>
+        <v>3.8055</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6532</v>
+        <v>6.5</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.173</v>
+        <v>2.6611</v>
       </c>
       <c r="L3" t="n">
-        <v>3.8262</v>
+        <v>3.8389</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5233</v>
+        <v>-0.915</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.0727</v>
+        <v>-0.8816000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4505</v>
+        <v>-0.0334</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5224</v>
+        <v>0.9702</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R3" t="n">
-        <v>3.4926</v>
+        <v>1.9403</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.681</v>
+        <v>-0.9772</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5501</v>
+        <v>-0.6873</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.1309</v>
+        <v>-0.2899</v>
       </c>
       <c r="V3" t="n">
-        <v>5.4223</v>
+        <v>2.4582</v>
       </c>
       <c r="W3" t="n">
-        <v>5.7895</v>
+        <v>1.8358</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3672</v>
+        <v>0.6224</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9557</v>
+        <v>1.7189</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1746</v>
+        <v>2.7742</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2189</v>
+        <v>-1.0554</v>
       </c>
       <c r="G4" t="n">
         <v>1.0407</v>
@@ -766,13 +766,13 @@
         <v>2.1344</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8611</v>
+        <v>-1.098</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4229</v>
+        <v>-0.8233</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4383</v>
+        <v>-0.2748</v>
       </c>
       <c r="V4" t="n">
         <v>0.6119</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4993</v>
+        <v>1.0481</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5414</v>
+        <v>-0.0198</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0407</v>
+        <v>1.0679</v>
       </c>
       <c r="G5" t="n">
         <v>0.4069</v>
@@ -844,13 +844,13 @@
         <v>2.5224</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7046</v>
+        <v>-1.1558</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1867</v>
+        <v>-0.6651</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5179</v>
+        <v>-0.4906</v>
       </c>
       <c r="V5" t="n">
         <v>0.2448</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5988</v>
+        <v>-0.9476</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2335</v>
+        <v>-0.4732</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3653</v>
+        <v>-0.4743</v>
       </c>
       <c r="G7" t="n">
         <v>0.2766</v>
@@ -1000,13 +1000,13 @@
         <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4365</v>
+        <v>0.0878</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5709</v>
+        <v>0.3311</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1343</v>
+        <v>-0.2434</v>
       </c>
       <c r="V7" t="n">
         <v>-1.506</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2909</v>
+        <v>-1.2181</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3773</v>
+        <v>-0.2772</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9137</v>
+        <v>-0.9409</v>
       </c>
       <c r="G8" t="n">
         <v>-1.4214</v>
@@ -1078,13 +1078,13 @@
         <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5397</v>
+        <v>-0.4669</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.424</v>
+        <v>-0.3239</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1157</v>
+        <v>-0.143</v>
       </c>
       <c r="V8" t="n">
         <v>0.2821</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3548</v>
+        <v>-1.4093</v>
       </c>
       <c r="E9" t="n">
         <v>-0.1405</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2143</v>
+        <v>-1.2688</v>
       </c>
       <c r="G9" t="n">
         <v>-1.0117</v>
@@ -1156,13 +1156,13 @@
         <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6431</v>
+        <v>-0.6976</v>
       </c>
       <c r="T9" t="n">
         <v>-0.2423</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4008</v>
+        <v>-0.4553</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2821</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5995</v>
+        <v>-1.7791</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7413</v>
+        <v>-1.2208</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8581</v>
+        <v>-0.5583</v>
       </c>
       <c r="G10" t="n">
         <v>0.8583</v>
@@ -1234,13 +1234,13 @@
         <v>2.1344</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0608</v>
+        <v>-1.2405</v>
       </c>
       <c r="T10" t="n">
-        <v>0.148</v>
+        <v>-0.3315</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2088</v>
+        <v>-0.909</v>
       </c>
       <c r="V10" t="n">
         <v>-1.591</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0489</v>
+        <v>-5.3361</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.1879</v>
+        <v>-4.7664</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1389</v>
+        <v>-0.5697</v>
       </c>
       <c r="G11" t="n">
         <v>2.8265</v>
@@ -1312,13 +1312,13 @@
         <v>3.1045</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6574</v>
+        <v>-0.9446</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1261</v>
+        <v>-0.7047</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4687</v>
+        <v>-0.24</v>
       </c>
       <c r="V11" t="n">
         <v>-1.591</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.2346</v>
+        <v>7.840400000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>9.392999999999997</v>
+        <v>9.998699999999999</v>
       </c>
       <c r="F12" t="n">
         <v>-2.1584</v>
@@ -1390,13 +1390,13 @@
         <v>17.463</v>
       </c>
       <c r="S12" t="n">
-        <v>-9.0398</v>
+        <v>-8.434199999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-5.081099999999999</v>
+        <v>-4.4755</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.9587</v>
+        <v>-3.9589</v>
       </c>
       <c r="V12" t="n">
         <v>4.049199999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.4443</v>
+        <v>4.3052</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8171</v>
+        <v>5.2175</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.3728</v>
+        <v>-0.9123</v>
       </c>
       <c r="G13" t="n">
         <v>4.7495</v>
@@ -1468,13 +1468,13 @@
         <v>2.5224</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0231</v>
+        <v>0.8378</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3006</v>
+        <v>0.0998</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2775</v>
+        <v>0.738</v>
       </c>
       <c r="V13" t="n">
         <v>-0.894</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. ALARCON ORTIZ</t>
+          <t>C. BARROS CONDES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7236</v>
+        <v>2.7526</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8036</v>
+        <v>3.1277</v>
       </c>
       <c r="F14" t="n">
-        <v>0.92</v>
+        <v>-0.3751</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3578</v>
+        <v>-2.4495</v>
       </c>
       <c r="H14" t="n">
-        <v>2.4189</v>
+        <v>0.0107</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.0611</v>
+        <v>-2.4602</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7397</v>
+        <v>0.5072</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6941</v>
+        <v>1.1823</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0456</v>
+        <v>-0.675</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3819</v>
+        <v>-2.9568</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2752</v>
+        <v>-1.1716</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.1067</v>
+        <v>-1.7852</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5821</v>
+        <v>2.9105</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5224</v>
+        <v>2.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0554</v>
+        <v>1.3498</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4878</v>
+        <v>0.1727</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5676</v>
+        <v>1.1771</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2716</v>
+        <v>0.9418</v>
       </c>
       <c r="W14" t="n">
-        <v>0.5164</v>
+        <v>2.4477</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.788</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8555</v>
+        <v>2.6802</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2769</v>
+        <v>0.2236</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1323</v>
+        <v>2.4566</v>
       </c>
       <c r="G15" t="n">
         <v>-0.8701</v>
@@ -1624,13 +1624,13 @@
         <v>2.1344</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0256</v>
+        <v>1.8503</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1962</v>
+        <v>0.6967</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8293</v>
+        <v>1.1536</v>
       </c>
       <c r="V15" t="n">
         <v>1.506</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. BARROS CONDES</t>
+          <t>M. ALARCON ORTIZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4207</v>
+        <v>2.327</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9265</v>
+        <v>1.6034</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5058</v>
+        <v>0.7236</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.4495</v>
+        <v>1.3578</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0107</v>
+        <v>2.4189</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.4602</v>
+        <v>-1.0611</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5072</v>
+        <v>2.7397</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1823</v>
+        <v>2.6941</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.675</v>
+        <v>0.0456</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.9568</v>
+        <v>-1.3819</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1716</v>
+        <v>-0.2752</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7852</v>
+        <v>-1.1067</v>
       </c>
       <c r="P16" t="n">
-        <v>2.9105</v>
+        <v>0.5821</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R16" t="n">
-        <v>2.9105</v>
+        <v>2.5224</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0179</v>
+        <v>1.6588</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0285</v>
+        <v>0.2876</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0465</v>
+        <v>1.3712</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9418</v>
+        <v>-1.2716</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4477</v>
+        <v>0.5164</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.506</v>
+        <v>-1.788</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2772</v>
+        <v>0.6593</v>
       </c>
       <c r="E17" t="n">
-        <v>1.4035</v>
+        <v>1.7038</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1263</v>
+        <v>-1.0445</v>
       </c>
       <c r="G17" t="n">
         <v>0.7617</v>
@@ -1780,13 +1780,13 @@
         <v>0.194</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.06660000000000001</v>
+        <v>0.3154</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0123</v>
+        <v>0.3126</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.079</v>
+        <v>0.0028</v>
       </c>
       <c r="V17" t="n">
         <v>-0.6119</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SAEZ BENITO</t>
+          <t>M. SANZ CÁMARA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.876</v>
+        <v>-0.6692</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5434</v>
+        <v>-0.1498</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.4194</v>
+        <v>-0.5194</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.6381</v>
+        <v>-2.0669</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.9246</v>
+        <v>-1.6782</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7135</v>
+        <v>-0.3887</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4397</v>
+        <v>-0.5415</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5437</v>
+        <v>-0.5643</v>
       </c>
       <c r="L18" t="n">
-        <v>0.104</v>
+        <v>0.0228</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1983</v>
+        <v>-1.5254</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3808</v>
+        <v>-1.1139</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8175</v>
+        <v>-0.4115</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3881</v>
+        <v>0.5821</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.5821</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2561</v>
+        <v>0.8157</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1653</v>
+        <v>0.3917</v>
       </c>
       <c r="U18" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.424</v>
       </c>
       <c r="V18" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.788</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.894</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SANZ CÁMARA</t>
+          <t>J. SAEZ BENITO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1941</v>
+        <v>-1.2402</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6503</v>
+        <v>1.0429</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5438</v>
+        <v>-2.2831</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.0669</v>
+        <v>-2.6381</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6782</v>
+        <v>-1.9246</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3887</v>
+        <v>-0.7135</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5415</v>
+        <v>-0.4397</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5643</v>
+        <v>-0.5437</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0228</v>
+        <v>0.104</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5254</v>
+        <v>-2.1983</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1139</v>
+        <v>-1.3808</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4115</v>
+        <v>-0.8175</v>
       </c>
       <c r="P19" t="n">
-        <v>0.5821</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
         <v>0.5821</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2907</v>
+        <v>0.8919</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1088</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3995</v>
+        <v>0.2271</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.788</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. SANTAMARIA LEON</t>
+          <t>S. RODRIGUEZ GREGORIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3224</v>
+        <v>-2.2335</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6708</v>
+        <v>-0.9509</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.9931</v>
+        <v>-1.2827</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0153</v>
+        <v>-2.266</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.7054</v>
+        <v>-0.3691</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6901</v>
+        <v>-1.8969</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6032999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2935</v>
+        <v>0.0659</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6901</v>
+        <v>0.005</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4119</v>
+        <v>-2.337</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4119</v>
+        <v>-0.435</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-1.9019</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.9702</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1406</v>
+        <v>-0.2212</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2741</v>
+        <v>-0.3054</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1335</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.4477</v>
+        <v>1.2239</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.4477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ GREGORIO</t>
+          <t>F. SANTAMARIA LEON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5583</v>
+        <v>-3.1232</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2512</v>
+        <v>-0.13</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3071</v>
+        <v>-2.9931</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.266</v>
+        <v>-1.0153</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.3691</v>
+        <v>-1.7054</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.8969</v>
+        <v>0.6901</v>
       </c>
       <c r="J21" t="n">
-        <v>0.07099999999999999</v>
+        <v>-0.6032999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0659</v>
+        <v>-1.2935</v>
       </c>
       <c r="L21" t="n">
-        <v>0.005</v>
+        <v>0.6901</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.337</v>
+        <v>-0.4119</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.435</v>
+        <v>-0.4119</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.9019</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9702</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.546</v>
+        <v>0.3398</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6057</v>
+        <v>0.4733</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0597</v>
+        <v>-0.1335</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2239</v>
+        <v>-2.4477</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2344</v>
+        <v>-3.9613</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3813</v>
+        <v>-2.081</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8531</v>
+        <v>-1.8803</v>
       </c>
       <c r="G22" t="n">
         <v>-1.4401</v>
@@ -2170,13 +2170,13 @@
         <v>0.194</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1759</v>
+        <v>0.4489</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1088</v>
+        <v>0.1915</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2847</v>
+        <v>0.2574</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2239</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7709</v>
+        <v>-7.3969</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.4469</v>
+        <v>-7.4489</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.324</v>
+        <v>0.0519</v>
       </c>
       <c r="G23" t="n">
         <v>-4.408</v>
@@ -2248,13 +2248,13 @@
         <v>2.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>3.7133</v>
+        <v>2.0872</v>
       </c>
       <c r="T23" t="n">
-        <v>2.9755</v>
+        <v>0.9735</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7378</v>
+        <v>1.1138</v>
       </c>
       <c r="V23" t="n">
         <v>-2.1657</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.234800000000001</v>
+        <v>-5.899999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>2.1583</v>
+        <v>2.158300000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.3931</v>
+        <v>-8.058399999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-10.285</v>
@@ -2311,10 +2311,10 @@
         <v>-17.9011</v>
       </c>
       <c r="N24" t="n">
-        <v>-8.280099999999999</v>
+        <v>-8.280100000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-9.621099999999998</v>
+        <v>-9.6211</v>
       </c>
       <c r="P24" t="n">
         <v>-1.9405</v>
@@ -2326,19 +2326,19 @@
         <v>15.5226</v>
       </c>
       <c r="S24" t="n">
-        <v>9.0398</v>
+        <v>10.3744</v>
       </c>
       <c r="T24" t="n">
         <v>3.9588</v>
       </c>
       <c r="U24" t="n">
-        <v>5.080900000000001</v>
+        <v>6.4156</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.049100000000001</v>
+        <v>-4.0491</v>
       </c>
       <c r="W24" t="n">
-        <v>8.046200000000002</v>
+        <v>8.046199999999999</v>
       </c>
       <c r="X24" t="n">
         <v>-12.0954</v>
